--- a/Data/2022_F013B4_CO_ISSWC/2022_F013B4_CO_ISSWC_CropCanopy.xlsx
+++ b/Data/2022_F013B4_CO_ISSWC/2022_F013B4_CO_ISSWC_CropCanopy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2022_F013B4_CO_ISSWC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F77BDA4B-81C9-43CD-A879-CB1F59256DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9014B42F-0135-4C6E-976E-FEFA8BBE69EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16470" yWindow="-19380" windowWidth="17805" windowHeight="18345" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16470" yWindow="-19380" windowWidth="17805" windowHeight="18345" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Height" sheetId="9" r:id="rId1"/>
@@ -53139,14 +53139,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ECA672C-8ED2-4A38-91F5-3D50AA22177A}">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="118" t="s">
         <v>227</v>
       </c>
@@ -53163,9 +53164,8 @@
         <v>231</v>
       </c>
       <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-    </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="119" t="s">
         <v>210</v>
       </c>
@@ -53178,11 +53178,11 @@
       <c r="D2" s="304">
         <v>124.25</v>
       </c>
-      <c r="E2" s="304">
-        <v>134.125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="E2" s="303">
+        <v>44695</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="119" t="s">
         <v>207</v>
       </c>
@@ -53195,11 +53195,11 @@
       <c r="D3" s="304">
         <v>122.5</v>
       </c>
-      <c r="E3" s="304">
-        <v>133.75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="E3" s="303">
+        <v>44695</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="119" t="s">
         <v>204</v>
       </c>
@@ -53212,11 +53212,11 @@
       <c r="D4" s="304">
         <v>124.1</v>
       </c>
-      <c r="E4" s="304">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="E4" s="303">
+        <v>44696</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="119" t="s">
         <v>201</v>
       </c>
@@ -53229,11 +53229,11 @@
       <c r="D5" s="304">
         <v>123</v>
       </c>
-      <c r="E5" s="304">
-        <v>133.75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="E5" s="303">
+        <v>44695</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="119" t="s">
         <v>198</v>
       </c>
@@ -53246,11 +53246,11 @@
       <c r="D6" s="304">
         <v>121.25</v>
       </c>
-      <c r="E6" s="304">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="E6" s="303">
+        <v>44693</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="119" t="s">
         <v>195</v>
       </c>
@@ -53263,11 +53263,11 @@
       <c r="D7" s="304">
         <v>121</v>
       </c>
-      <c r="E7" s="304">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="E7" s="303">
+        <v>44694</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="119" t="s">
         <v>192</v>
       </c>
@@ -53280,11 +53280,11 @@
       <c r="D8" s="304">
         <v>120.5</v>
       </c>
-      <c r="E8" s="304">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="E8" s="303">
+        <v>44692</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="119" t="s">
         <v>189</v>
       </c>
@@ -53297,11 +53297,11 @@
       <c r="D9" s="304">
         <v>120.8</v>
       </c>
-      <c r="E9" s="304">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="E9" s="303">
+        <v>44693</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="119" t="s">
         <v>186</v>
       </c>
@@ -53314,11 +53314,11 @@
       <c r="D10" s="304">
         <v>124.25</v>
       </c>
-      <c r="E10" s="304">
-        <v>134.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="E10" s="303">
+        <v>44696</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="119" t="s">
         <v>183</v>
       </c>
@@ -53331,11 +53331,11 @@
       <c r="D11" s="304">
         <v>121.35714285714286</v>
       </c>
-      <c r="E11" s="304">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="E11" s="303">
+        <v>44695</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="119" t="s">
         <v>180</v>
       </c>
@@ -53348,11 +53348,11 @@
       <c r="D12" s="304">
         <v>120.8</v>
       </c>
-      <c r="E12" s="304">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="E12" s="303">
+        <v>44695</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="119" t="s">
         <v>177</v>
       </c>
@@ -53365,11 +53365,11 @@
       <c r="D13" s="304">
         <v>124.125</v>
       </c>
-      <c r="E13" s="304">
-        <v>135.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="E13" s="303">
+        <v>44697</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="119" t="s">
         <v>174</v>
       </c>
@@ -53382,11 +53382,11 @@
       <c r="D14" s="304">
         <v>120.8</v>
       </c>
-      <c r="E14" s="304">
-        <v>132.25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="E14" s="303">
+        <v>44693</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="119" t="s">
         <v>171</v>
       </c>
@@ -53399,11 +53399,11 @@
       <c r="D15" s="304">
         <v>121.25</v>
       </c>
-      <c r="E15" s="304">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="E15" s="303">
+        <v>44694</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="119" t="s">
         <v>168</v>
       </c>
@@ -53416,8 +53416,8 @@
       <c r="D16" s="304">
         <v>122.16666666666667</v>
       </c>
-      <c r="E16" s="304">
-        <v>133.5</v>
+      <c r="E16" s="303">
+        <v>44695</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53433,8 +53433,8 @@
       <c r="D17" s="304">
         <v>120.5</v>
       </c>
-      <c r="E17" s="304">
-        <v>132.5</v>
+      <c r="E17" s="303">
+        <v>44694</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53450,8 +53450,8 @@
       <c r="D18" s="304">
         <v>121.1</v>
       </c>
-      <c r="E18" s="304">
-        <v>133.375</v>
+      <c r="E18" s="303">
+        <v>44694</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53467,8 +53467,8 @@
       <c r="D19" s="304">
         <v>121.25</v>
       </c>
-      <c r="E19" s="304">
-        <v>132.5</v>
+      <c r="E19" s="303">
+        <v>44694</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53484,8 +53484,8 @@
       <c r="D20" s="304">
         <v>122</v>
       </c>
-      <c r="E20" s="304">
-        <v>132.25</v>
+      <c r="E20" s="303">
+        <v>44693</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53501,8 +53501,8 @@
       <c r="D21" s="304">
         <v>120.5</v>
       </c>
-      <c r="E21" s="304">
-        <v>133.375</v>
+      <c r="E21" s="303">
+        <v>44694</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53518,8 +53518,8 @@
       <c r="D22" s="304">
         <v>121.1</v>
       </c>
-      <c r="E22" s="304">
-        <v>134.5</v>
+      <c r="E22" s="303">
+        <v>44696</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53535,8 +53535,8 @@
       <c r="D23" s="304">
         <v>123.5</v>
       </c>
-      <c r="E23" s="304">
-        <v>136.5</v>
+      <c r="E23" s="303">
+        <v>44698</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53552,8 +53552,8 @@
       <c r="D24" s="304">
         <v>122.5</v>
       </c>
-      <c r="E24" s="304">
-        <v>134.5</v>
+      <c r="E24" s="303">
+        <v>44696</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53569,8 +53569,8 @@
       <c r="D25" s="304">
         <v>125</v>
       </c>
-      <c r="E25" s="304">
-        <v>136.75</v>
+      <c r="E25" s="303">
+        <v>44698</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53586,8 +53586,8 @@
       <c r="D26" s="304">
         <v>122.25</v>
       </c>
-      <c r="E26" s="304">
-        <v>133.75</v>
+      <c r="E26" s="303">
+        <v>44695</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53603,8 +53603,8 @@
       <c r="D27" s="304">
         <v>122</v>
       </c>
-      <c r="E27" s="304">
-        <v>133</v>
+      <c r="E27" s="303">
+        <v>44694</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53620,8 +53620,8 @@
       <c r="D28" s="304">
         <v>120.75</v>
       </c>
-      <c r="E28" s="304">
-        <v>131.875</v>
+      <c r="E28" s="303">
+        <v>44693</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53637,8 +53637,8 @@
       <c r="D29" s="304">
         <v>121.625</v>
       </c>
-      <c r="E29" s="304">
-        <v>134.5</v>
+      <c r="E29" s="303">
+        <v>44696</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53654,8 +53654,8 @@
       <c r="D30" s="304">
         <v>124.25</v>
       </c>
-      <c r="E30" s="304">
-        <v>135.25</v>
+      <c r="E30" s="303">
+        <v>44696</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53671,8 +53671,8 @@
       <c r="D31" s="304">
         <v>122.75</v>
       </c>
-      <c r="E31" s="304">
-        <v>134.5</v>
+      <c r="E31" s="303">
+        <v>44696</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53688,8 +53688,8 @@
       <c r="D32" s="304">
         <v>122.25</v>
       </c>
-      <c r="E32" s="304">
-        <v>134.875</v>
+      <c r="E32" s="303">
+        <v>44696</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53705,8 +53705,8 @@
       <c r="D33" s="304">
         <v>123</v>
       </c>
-      <c r="E33" s="304">
-        <v>136.75</v>
+      <c r="E33" s="303">
+        <v>44698</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53722,8 +53722,8 @@
       <c r="D34" s="304">
         <v>125</v>
       </c>
-      <c r="E34" s="304">
-        <v>136</v>
+      <c r="E34" s="303">
+        <v>44697</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53739,8 +53739,8 @@
       <c r="D35" s="304">
         <v>122.83333333333333</v>
       </c>
-      <c r="E35" s="304">
-        <v>134.5</v>
+      <c r="E35" s="303">
+        <v>44696</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53756,8 +53756,8 @@
       <c r="D36" s="304">
         <v>125.8</v>
       </c>
-      <c r="E36" s="304">
-        <v>135.25</v>
+      <c r="E36" s="303">
+        <v>44696</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53773,8 +53773,8 @@
       <c r="D37" s="304">
         <v>122.25</v>
       </c>
-      <c r="E37" s="304">
-        <v>137.16666666666666</v>
+      <c r="E37" s="303">
+        <v>44698</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53790,8 +53790,8 @@
       <c r="D38" s="304">
         <v>122</v>
       </c>
-      <c r="E38" s="304">
-        <v>134</v>
+      <c r="E38" s="303">
+        <v>44695</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53807,8 +53807,8 @@
       <c r="D39" s="304">
         <v>121.625</v>
       </c>
-      <c r="E39" s="304">
-        <v>135.5</v>
+      <c r="E39" s="303">
+        <v>44697</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53824,8 +53824,8 @@
       <c r="D40" s="304">
         <v>122.3</v>
       </c>
-      <c r="E40" s="304">
-        <v>133.5</v>
+      <c r="E40" s="303">
+        <v>44695</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53841,8 +53841,8 @@
       <c r="D41" s="304">
         <v>121</v>
       </c>
-      <c r="E41" s="304">
-        <v>133</v>
+      <c r="E41" s="303">
+        <v>44694</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53858,8 +53858,8 @@
       <c r="D42" s="304">
         <v>122</v>
       </c>
-      <c r="E42" s="304">
-        <v>132</v>
+      <c r="E42" s="303">
+        <v>44693</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53875,8 +53875,8 @@
       <c r="D43" s="304">
         <v>121.5</v>
       </c>
-      <c r="E43" s="304">
-        <v>134.5</v>
+      <c r="E43" s="303">
+        <v>44696</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53892,8 +53892,8 @@
       <c r="D44" s="304">
         <v>121.25</v>
       </c>
-      <c r="E44" s="304">
-        <v>132.4</v>
+      <c r="E44" s="303">
+        <v>44693</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53909,8 +53909,8 @@
       <c r="D45" s="304">
         <v>121.625</v>
       </c>
-      <c r="E45" s="304">
-        <v>133.75</v>
+      <c r="E45" s="303">
+        <v>44695</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53926,8 +53926,8 @@
       <c r="D46" s="304">
         <v>125.4</v>
       </c>
-      <c r="E46" s="304">
-        <v>134.5</v>
+      <c r="E46" s="303">
+        <v>44696</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53943,8 +53943,8 @@
       <c r="D47" s="304">
         <v>123</v>
       </c>
-      <c r="E47" s="304">
-        <v>137.4</v>
+      <c r="E47" s="303">
+        <v>44698</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53960,8 +53960,8 @@
       <c r="D48" s="304">
         <v>127</v>
       </c>
-      <c r="E48" s="304">
-        <v>144.5</v>
+      <c r="E48" s="303">
+        <v>44706</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -53977,12 +53977,12 @@
       <c r="D49" s="304">
         <v>122.75</v>
       </c>
-      <c r="E49" s="304">
-        <v>139.5</v>
+      <c r="E49" s="303">
+        <v>44701</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E49">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D49">
     <sortCondition ref="A2:A49"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -53996,7 +53996,8 @@
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -54054,8 +54055,8 @@
       <c r="D2" s="304">
         <v>124.25</v>
       </c>
-      <c r="E2" s="304">
-        <v>134.125</v>
+      <c r="E2" s="303">
+        <v>44695</v>
       </c>
       <c r="F2" s="302">
         <v>8.5</v>
@@ -54095,8 +54096,8 @@
       <c r="D3" s="304">
         <v>122.5</v>
       </c>
-      <c r="E3" s="304">
-        <v>133.75</v>
+      <c r="E3" s="303">
+        <v>44695</v>
       </c>
       <c r="F3" s="302">
         <v>7.333333333333333</v>
@@ -54136,8 +54137,8 @@
       <c r="D4" s="304">
         <v>124.1</v>
       </c>
-      <c r="E4" s="304">
-        <v>135</v>
+      <c r="E4" s="303">
+        <v>44696</v>
       </c>
       <c r="F4" s="302">
         <v>8</v>
@@ -54177,8 +54178,8 @@
       <c r="D5" s="304">
         <v>123</v>
       </c>
-      <c r="E5" s="304">
-        <v>133.75</v>
+      <c r="E5" s="303">
+        <v>44695</v>
       </c>
       <c r="F5" s="302">
         <v>8.3333333333333339</v>
@@ -54218,8 +54219,8 @@
       <c r="D6" s="304">
         <v>121.25</v>
       </c>
-      <c r="E6" s="304">
-        <v>132</v>
+      <c r="E6" s="303">
+        <v>44693</v>
       </c>
       <c r="F6" s="302">
         <v>8.6666666666666661</v>
@@ -54259,8 +54260,8 @@
       <c r="D7" s="304">
         <v>121</v>
       </c>
-      <c r="E7" s="304">
-        <v>133</v>
+      <c r="E7" s="303">
+        <v>44694</v>
       </c>
       <c r="F7" s="302">
         <v>8.2222222222222214</v>
@@ -54300,8 +54301,8 @@
       <c r="D8" s="304">
         <v>120.5</v>
       </c>
-      <c r="E8" s="304">
-        <v>131</v>
+      <c r="E8" s="303">
+        <v>44692</v>
       </c>
       <c r="F8" s="302">
         <v>8.4444444444444446</v>
@@ -54341,8 +54342,8 @@
       <c r="D9" s="304">
         <v>120.8</v>
       </c>
-      <c r="E9" s="304">
-        <v>132</v>
+      <c r="E9" s="303">
+        <v>44693</v>
       </c>
       <c r="F9" s="302">
         <v>7.333333333333333</v>
@@ -54382,8 +54383,8 @@
       <c r="D10" s="304">
         <v>124.25</v>
       </c>
-      <c r="E10" s="304">
-        <v>134.5</v>
+      <c r="E10" s="303">
+        <v>44696</v>
       </c>
       <c r="F10" s="302">
         <v>7.7777777777777777</v>
@@ -54423,8 +54424,8 @@
       <c r="D11" s="304">
         <v>121.35714285714286</v>
       </c>
-      <c r="E11" s="304">
-        <v>134</v>
+      <c r="E11" s="303">
+        <v>44695</v>
       </c>
       <c r="F11" s="302">
         <v>8.4444444444444446</v>
@@ -54464,8 +54465,8 @@
       <c r="D12" s="304">
         <v>120.8</v>
       </c>
-      <c r="E12" s="304">
-        <v>134</v>
+      <c r="E12" s="303">
+        <v>44695</v>
       </c>
       <c r="F12" s="302">
         <v>8.7777777777777786</v>
@@ -54505,8 +54506,8 @@
       <c r="D13" s="304">
         <v>124.125</v>
       </c>
-      <c r="E13" s="304">
-        <v>135.5</v>
+      <c r="E13" s="303">
+        <v>44697</v>
       </c>
       <c r="F13" s="302">
         <v>8.8888888888888893</v>
@@ -54546,8 +54547,8 @@
       <c r="D14" s="304">
         <v>120.8</v>
       </c>
-      <c r="E14" s="304">
-        <v>132.25</v>
+      <c r="E14" s="303">
+        <v>44693</v>
       </c>
       <c r="F14" s="302">
         <v>8.4444444444444446</v>
@@ -54587,8 +54588,8 @@
       <c r="D15" s="304">
         <v>121.25</v>
       </c>
-      <c r="E15" s="304">
-        <v>133</v>
+      <c r="E15" s="303">
+        <v>44694</v>
       </c>
       <c r="F15" s="302">
         <v>9.3333333333333339</v>
@@ -54628,8 +54629,8 @@
       <c r="D16" s="304">
         <v>122.16666666666667</v>
       </c>
-      <c r="E16" s="304">
-        <v>133.5</v>
+      <c r="E16" s="303">
+        <v>44695</v>
       </c>
       <c r="F16" s="302">
         <v>9.5555555555555554</v>
@@ -54669,8 +54670,8 @@
       <c r="D17" s="304">
         <v>120.5</v>
       </c>
-      <c r="E17" s="304">
-        <v>132.5</v>
+      <c r="E17" s="303">
+        <v>44694</v>
       </c>
       <c r="F17" s="302">
         <v>8.4444444444444446</v>
@@ -54710,8 +54711,8 @@
       <c r="D18" s="304">
         <v>121.1</v>
       </c>
-      <c r="E18" s="304">
-        <v>133.375</v>
+      <c r="E18" s="303">
+        <v>44694</v>
       </c>
       <c r="F18" s="302">
         <v>7.4444444444444446</v>
@@ -54751,8 +54752,8 @@
       <c r="D19" s="304">
         <v>121.25</v>
       </c>
-      <c r="E19" s="304">
-        <v>132.5</v>
+      <c r="E19" s="303">
+        <v>44694</v>
       </c>
       <c r="F19" s="302">
         <v>7.8888888888888893</v>
@@ -54792,8 +54793,8 @@
       <c r="D20" s="304">
         <v>122</v>
       </c>
-      <c r="E20" s="304">
-        <v>132.25</v>
+      <c r="E20" s="303">
+        <v>44693</v>
       </c>
       <c r="F20" s="302">
         <v>7.666666666666667</v>
@@ -54833,8 +54834,8 @@
       <c r="D21" s="304">
         <v>120.5</v>
       </c>
-      <c r="E21" s="304">
-        <v>133.375</v>
+      <c r="E21" s="303">
+        <v>44694</v>
       </c>
       <c r="F21" s="302">
         <v>7.5555555555555554</v>
@@ -54874,8 +54875,8 @@
       <c r="D22" s="304">
         <v>121.1</v>
       </c>
-      <c r="E22" s="304">
-        <v>134.5</v>
+      <c r="E22" s="303">
+        <v>44696</v>
       </c>
       <c r="F22" s="302">
         <v>8.7777777777777786</v>
@@ -54915,8 +54916,8 @@
       <c r="D23" s="304">
         <v>123.5</v>
       </c>
-      <c r="E23" s="304">
-        <v>136.5</v>
+      <c r="E23" s="303">
+        <v>44698</v>
       </c>
       <c r="F23" s="302">
         <v>7.4444444444444446</v>
@@ -54956,8 +54957,8 @@
       <c r="D24" s="304">
         <v>122.5</v>
       </c>
-      <c r="E24" s="304">
-        <v>134.5</v>
+      <c r="E24" s="303">
+        <v>44696</v>
       </c>
       <c r="F24" s="302">
         <v>8.1111111111111107</v>
@@ -54997,8 +54998,8 @@
       <c r="D25" s="304">
         <v>125</v>
       </c>
-      <c r="E25" s="304">
-        <v>136.75</v>
+      <c r="E25" s="303">
+        <v>44698</v>
       </c>
       <c r="F25" s="302">
         <v>8</v>
@@ -55038,8 +55039,8 @@
       <c r="D26" s="304">
         <v>122.25</v>
       </c>
-      <c r="E26" s="304">
-        <v>133.75</v>
+      <c r="E26" s="303">
+        <v>44695</v>
       </c>
       <c r="F26" s="302">
         <v>6.4444444444444446</v>
@@ -55079,8 +55080,8 @@
       <c r="D27" s="304">
         <v>122</v>
       </c>
-      <c r="E27" s="304">
-        <v>133</v>
+      <c r="E27" s="303">
+        <v>44694</v>
       </c>
       <c r="F27" s="302">
         <v>7.5555555555555554</v>
@@ -55120,8 +55121,8 @@
       <c r="D28" s="304">
         <v>120.75</v>
       </c>
-      <c r="E28" s="304">
-        <v>131.875</v>
+      <c r="E28" s="303">
+        <v>44693</v>
       </c>
       <c r="F28" s="302">
         <v>8.3333333333333339</v>
@@ -55161,8 +55162,8 @@
       <c r="D29" s="304">
         <v>121.625</v>
       </c>
-      <c r="E29" s="304">
-        <v>134.5</v>
+      <c r="E29" s="303">
+        <v>44696</v>
       </c>
       <c r="F29" s="302">
         <v>8.3333333333333339</v>
@@ -55202,8 +55203,8 @@
       <c r="D30" s="304">
         <v>124.25</v>
       </c>
-      <c r="E30" s="304">
-        <v>135.25</v>
+      <c r="E30" s="303">
+        <v>44696</v>
       </c>
       <c r="F30" s="302">
         <v>7.1111111111111107</v>
@@ -55243,8 +55244,8 @@
       <c r="D31" s="304">
         <v>122.75</v>
       </c>
-      <c r="E31" s="304">
-        <v>134.5</v>
+      <c r="E31" s="303">
+        <v>44696</v>
       </c>
       <c r="F31" s="302">
         <v>9.1111111111111107</v>
@@ -55284,8 +55285,8 @@
       <c r="D32" s="304">
         <v>122.25</v>
       </c>
-      <c r="E32" s="304">
-        <v>134.875</v>
+      <c r="E32" s="303">
+        <v>44696</v>
       </c>
       <c r="F32" s="302">
         <v>9.2222222222222214</v>
@@ -55325,8 +55326,8 @@
       <c r="D33" s="304">
         <v>123</v>
       </c>
-      <c r="E33" s="304">
-        <v>136.75</v>
+      <c r="E33" s="303">
+        <v>44698</v>
       </c>
       <c r="F33" s="302">
         <v>8.7777777777777786</v>
@@ -55366,8 +55367,8 @@
       <c r="D34" s="304">
         <v>125</v>
       </c>
-      <c r="E34" s="304">
-        <v>136</v>
+      <c r="E34" s="303">
+        <v>44697</v>
       </c>
       <c r="F34" s="302">
         <v>8.1111111111111107</v>
@@ -55407,8 +55408,8 @@
       <c r="D35" s="304">
         <v>122.83333333333333</v>
       </c>
-      <c r="E35" s="304">
-        <v>134.5</v>
+      <c r="E35" s="303">
+        <v>44696</v>
       </c>
       <c r="F35" s="302">
         <v>8.7777777777777786</v>
@@ -55448,8 +55449,8 @@
       <c r="D36" s="304">
         <v>125.8</v>
       </c>
-      <c r="E36" s="304">
-        <v>135.25</v>
+      <c r="E36" s="303">
+        <v>44696</v>
       </c>
       <c r="F36" s="302">
         <v>8.2222222222222214</v>
@@ -55489,8 +55490,8 @@
       <c r="D37" s="304">
         <v>122.25</v>
       </c>
-      <c r="E37" s="304">
-        <v>137.16666666666666</v>
+      <c r="E37" s="303">
+        <v>44698</v>
       </c>
       <c r="F37" s="302">
         <v>8</v>
@@ -55530,8 +55531,8 @@
       <c r="D38" s="304">
         <v>122</v>
       </c>
-      <c r="E38" s="304">
-        <v>134</v>
+      <c r="E38" s="303">
+        <v>44695</v>
       </c>
       <c r="F38" s="302">
         <v>8.1111111111111107</v>
@@ -55571,8 +55572,8 @@
       <c r="D39" s="304">
         <v>121.625</v>
       </c>
-      <c r="E39" s="304">
-        <v>135.5</v>
+      <c r="E39" s="303">
+        <v>44697</v>
       </c>
       <c r="F39" s="302">
         <v>8.2222222222222214</v>
@@ -55612,8 +55613,8 @@
       <c r="D40" s="304">
         <v>122.3</v>
       </c>
-      <c r="E40" s="304">
-        <v>133.5</v>
+      <c r="E40" s="303">
+        <v>44695</v>
       </c>
       <c r="F40" s="302">
         <v>7.4444444444444446</v>
@@ -55653,8 +55654,8 @@
       <c r="D41" s="304">
         <v>121</v>
       </c>
-      <c r="E41" s="304">
-        <v>133</v>
+      <c r="E41" s="303">
+        <v>44694</v>
       </c>
       <c r="F41" s="302">
         <v>7</v>
@@ -55694,8 +55695,8 @@
       <c r="D42" s="304">
         <v>122</v>
       </c>
-      <c r="E42" s="304">
-        <v>132</v>
+      <c r="E42" s="303">
+        <v>44693</v>
       </c>
       <c r="F42" s="302">
         <v>8.1111111111111107</v>
@@ -55735,8 +55736,8 @@
       <c r="D43" s="304">
         <v>121.5</v>
       </c>
-      <c r="E43" s="304">
-        <v>134.5</v>
+      <c r="E43" s="303">
+        <v>44696</v>
       </c>
       <c r="F43" s="302">
         <v>8.4444444444444446</v>
@@ -55776,8 +55777,8 @@
       <c r="D44" s="304">
         <v>121.25</v>
       </c>
-      <c r="E44" s="304">
-        <v>132.4</v>
+      <c r="E44" s="303">
+        <v>44693</v>
       </c>
       <c r="F44" s="302">
         <v>8.5555555555555554</v>
@@ -55817,8 +55818,8 @@
       <c r="D45" s="304">
         <v>121.625</v>
       </c>
-      <c r="E45" s="304">
-        <v>133.75</v>
+      <c r="E45" s="303">
+        <v>44695</v>
       </c>
       <c r="F45" s="302">
         <v>7.4444444444444446</v>
@@ -55858,8 +55859,8 @@
       <c r="D46" s="304">
         <v>125.4</v>
       </c>
-      <c r="E46" s="304">
-        <v>134.5</v>
+      <c r="E46" s="303">
+        <v>44696</v>
       </c>
       <c r="F46" s="302">
         <v>7.2222222222222223</v>
@@ -55899,8 +55900,8 @@
       <c r="D47" s="304">
         <v>123</v>
       </c>
-      <c r="E47" s="304">
-        <v>137.4</v>
+      <c r="E47" s="303">
+        <v>44698</v>
       </c>
       <c r="F47" s="302">
         <v>8.6666666666666661</v>
@@ -55940,8 +55941,8 @@
       <c r="D48" s="304">
         <v>127</v>
       </c>
-      <c r="E48" s="304">
-        <v>144.5</v>
+      <c r="E48" s="303">
+        <v>44706</v>
       </c>
       <c r="F48" s="302">
         <v>9.3333333333333339</v>
@@ -55981,8 +55982,8 @@
       <c r="D49" s="304">
         <v>122.75</v>
       </c>
-      <c r="E49" s="304">
-        <v>139.5</v>
+      <c r="E49" s="303">
+        <v>44701</v>
       </c>
       <c r="F49" s="302">
         <v>8.3333333333333339</v>

--- a/Data/2022_F013B4_CO_ISSWC/2022_F013B4_CO_ISSWC_CropCanopy.xlsx
+++ b/Data/2022_F013B4_CO_ISSWC/2022_F013B4_CO_ISSWC_CropCanopy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2022_F013B4_CO_ISSWC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBEBFEB9-65BE-4DF6-A9C5-903F4A058882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A30AA750-5C89-4988-9458-5235ED34944C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1470" yWindow="-24900" windowWidth="17805" windowHeight="20370" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1635" yWindow="-20730" windowWidth="18030" windowHeight="16230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Height" sheetId="9" r:id="rId1"/>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4220" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4220" uniqueCount="320">
   <si>
     <t>01-</t>
   </si>
@@ -995,9 +995,6 @@
   </si>
   <si>
     <t>31 May &amp; 6 June 2022</t>
-  </si>
-  <si>
-    <t>PLAPD</t>
   </si>
   <si>
     <t>Average</t>
@@ -2595,91 +2592,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="20" fontId="36" fillId="0" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="26" fillId="6" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="37" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="36" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="34" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="33" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="8" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="36" fillId="8" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="26" fillId="7" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="37" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="36" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="36" fillId="6" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="31" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="7" borderId="38" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="36" fillId="8" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="26" fillId="8" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="36" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="33" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="6" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2708,6 +2624,87 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="7" borderId="38" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="37" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="36" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="34" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="33" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="36" fillId="6" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="31" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="26" fillId="6" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="37" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="36" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="26" fillId="7" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="36" fillId="8" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="8" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="26" fillId="8" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="36" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="33" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="36" fillId="8" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -9726,60 +9723,60 @@
       <c r="D11" s="202">
         <v>44680</v>
       </c>
-      <c r="E11" s="286">
+      <c r="E11" s="294">
         <v>44683</v>
       </c>
-      <c r="F11" s="284"/>
-      <c r="G11" s="275">
+      <c r="F11" s="291"/>
+      <c r="G11" s="290">
         <v>44684</v>
       </c>
-      <c r="H11" s="284"/>
-      <c r="I11" s="286">
+      <c r="H11" s="291"/>
+      <c r="I11" s="294">
         <v>44685</v>
       </c>
-      <c r="J11" s="288"/>
-      <c r="K11" s="275">
+      <c r="J11" s="296"/>
+      <c r="K11" s="290">
         <v>44686</v>
       </c>
-      <c r="L11" s="284"/>
-      <c r="M11" s="266">
+      <c r="L11" s="291"/>
+      <c r="M11" s="285">
         <v>44690</v>
       </c>
-      <c r="N11" s="267"/>
-      <c r="O11" s="268"/>
-      <c r="P11" s="275">
+      <c r="N11" s="286"/>
+      <c r="O11" s="287"/>
+      <c r="P11" s="290">
         <v>44691</v>
       </c>
-      <c r="Q11" s="276"/>
-      <c r="R11" s="277"/>
-      <c r="S11" s="266">
+      <c r="Q11" s="273"/>
+      <c r="R11" s="274"/>
+      <c r="S11" s="285">
         <v>44694</v>
       </c>
-      <c r="T11" s="267"/>
-      <c r="U11" s="268"/>
-      <c r="V11" s="281">
+      <c r="T11" s="286"/>
+      <c r="U11" s="287"/>
+      <c r="V11" s="272">
         <v>44697</v>
       </c>
-      <c r="W11" s="276"/>
-      <c r="X11" s="277"/>
-      <c r="Y11" s="266">
+      <c r="W11" s="273"/>
+      <c r="X11" s="274"/>
+      <c r="Y11" s="285">
         <v>44700</v>
       </c>
-      <c r="Z11" s="267"/>
-      <c r="AA11" s="268"/>
-      <c r="AB11" s="281">
+      <c r="Z11" s="286"/>
+      <c r="AA11" s="287"/>
+      <c r="AB11" s="272">
         <v>44704</v>
       </c>
-      <c r="AC11" s="276"/>
-      <c r="AD11" s="277"/>
-      <c r="AE11" s="266">
+      <c r="AC11" s="273"/>
+      <c r="AD11" s="274"/>
+      <c r="AE11" s="285">
         <v>44707</v>
       </c>
-      <c r="AF11" s="267"/>
-      <c r="AG11" s="268"/>
-      <c r="AH11" s="281"/>
-      <c r="AI11" s="276"/>
-      <c r="AJ11" s="277"/>
+      <c r="AF11" s="286"/>
+      <c r="AG11" s="287"/>
+      <c r="AH11" s="272"/>
+      <c r="AI11" s="273"/>
+      <c r="AJ11" s="274"/>
     </row>
     <row r="12" spans="1:36" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="201"/>
@@ -9789,60 +9786,60 @@
       <c r="D12" s="200">
         <v>119</v>
       </c>
-      <c r="E12" s="287">
+      <c r="E12" s="295">
         <v>122</v>
       </c>
-      <c r="F12" s="263"/>
+      <c r="F12" s="280"/>
       <c r="G12" s="278">
         <v>123</v>
       </c>
-      <c r="H12" s="263"/>
-      <c r="I12" s="287">
+      <c r="H12" s="280"/>
+      <c r="I12" s="295">
         <v>124</v>
       </c>
-      <c r="J12" s="289"/>
+      <c r="J12" s="297"/>
       <c r="K12" s="278">
         <v>125</v>
       </c>
-      <c r="L12" s="263"/>
-      <c r="M12" s="269">
+      <c r="L12" s="280"/>
+      <c r="M12" s="275">
         <v>129</v>
       </c>
-      <c r="N12" s="270"/>
-      <c r="O12" s="271"/>
+      <c r="N12" s="276"/>
+      <c r="O12" s="277"/>
       <c r="P12" s="278">
         <v>130</v>
       </c>
-      <c r="Q12" s="262"/>
-      <c r="R12" s="263"/>
-      <c r="S12" s="269">
+      <c r="Q12" s="279"/>
+      <c r="R12" s="280"/>
+      <c r="S12" s="275">
         <v>133</v>
       </c>
-      <c r="T12" s="270"/>
-      <c r="U12" s="271"/>
+      <c r="T12" s="276"/>
+      <c r="U12" s="277"/>
       <c r="V12" s="278">
         <v>136</v>
       </c>
-      <c r="W12" s="262"/>
-      <c r="X12" s="263"/>
-      <c r="Y12" s="269">
+      <c r="W12" s="279"/>
+      <c r="X12" s="280"/>
+      <c r="Y12" s="275">
         <v>139</v>
       </c>
-      <c r="Z12" s="270"/>
-      <c r="AA12" s="271"/>
+      <c r="Z12" s="276"/>
+      <c r="AA12" s="277"/>
       <c r="AB12" s="278">
         <v>143</v>
       </c>
-      <c r="AC12" s="262"/>
-      <c r="AD12" s="263"/>
-      <c r="AE12" s="269">
+      <c r="AC12" s="279"/>
+      <c r="AD12" s="280"/>
+      <c r="AE12" s="275">
         <v>146</v>
       </c>
-      <c r="AF12" s="270"/>
-      <c r="AG12" s="271"/>
+      <c r="AF12" s="276"/>
+      <c r="AG12" s="277"/>
       <c r="AH12" s="278"/>
-      <c r="AI12" s="262"/>
-      <c r="AJ12" s="263"/>
+      <c r="AI12" s="279"/>
+      <c r="AJ12" s="280"/>
     </row>
     <row r="13" spans="1:36" s="197" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="199"/>
@@ -9852,99 +9849,99 @@
       <c r="D13" s="198" t="s">
         <v>290</v>
       </c>
-      <c r="E13" s="272" t="s">
+      <c r="E13" s="293" t="s">
         <v>51</v>
       </c>
-      <c r="F13" s="263"/>
-      <c r="G13" s="261" t="s">
+      <c r="F13" s="280"/>
+      <c r="G13" s="282" t="s">
         <v>51</v>
       </c>
-      <c r="H13" s="263"/>
-      <c r="I13" s="272" t="s">
+      <c r="H13" s="280"/>
+      <c r="I13" s="293" t="s">
         <v>51</v>
       </c>
-      <c r="J13" s="263"/>
-      <c r="K13" s="261" t="s">
+      <c r="J13" s="280"/>
+      <c r="K13" s="282" t="s">
         <v>51</v>
       </c>
-      <c r="L13" s="263"/>
-      <c r="M13" s="274" t="s">
+      <c r="L13" s="280"/>
+      <c r="M13" s="281" t="s">
         <v>51</v>
       </c>
-      <c r="N13" s="270"/>
-      <c r="O13" s="271"/>
-      <c r="P13" s="261" t="s">
+      <c r="N13" s="276"/>
+      <c r="O13" s="277"/>
+      <c r="P13" s="282" t="s">
         <v>51</v>
       </c>
-      <c r="Q13" s="262"/>
-      <c r="R13" s="263"/>
-      <c r="S13" s="274" t="s">
+      <c r="Q13" s="279"/>
+      <c r="R13" s="280"/>
+      <c r="S13" s="281" t="s">
         <v>51</v>
       </c>
-      <c r="T13" s="270"/>
-      <c r="U13" s="271"/>
-      <c r="V13" s="261" t="s">
+      <c r="T13" s="276"/>
+      <c r="U13" s="277"/>
+      <c r="V13" s="282" t="s">
         <v>51</v>
       </c>
-      <c r="W13" s="262"/>
-      <c r="X13" s="263"/>
-      <c r="Y13" s="274" t="s">
+      <c r="W13" s="279"/>
+      <c r="X13" s="280"/>
+      <c r="Y13" s="281" t="s">
         <v>51</v>
       </c>
-      <c r="Z13" s="270"/>
-      <c r="AA13" s="271"/>
-      <c r="AB13" s="261" t="s">
+      <c r="Z13" s="276"/>
+      <c r="AA13" s="277"/>
+      <c r="AB13" s="282" t="s">
         <v>51</v>
       </c>
-      <c r="AC13" s="262"/>
-      <c r="AD13" s="263"/>
-      <c r="AE13" s="274" t="s">
+      <c r="AC13" s="279"/>
+      <c r="AD13" s="280"/>
+      <c r="AE13" s="281" t="s">
         <v>51</v>
       </c>
-      <c r="AF13" s="270"/>
-      <c r="AG13" s="271"/>
-      <c r="AH13" s="261" t="s">
+      <c r="AF13" s="276"/>
+      <c r="AG13" s="277"/>
+      <c r="AH13" s="282" t="s">
         <v>51</v>
       </c>
-      <c r="AI13" s="262"/>
-      <c r="AJ13" s="263"/>
+      <c r="AI13" s="279"/>
+      <c r="AJ13" s="280"/>
     </row>
     <row r="14" spans="1:36" s="118" customFormat="1" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="194"/>
       <c r="B14" s="193"/>
       <c r="C14" s="193"/>
       <c r="D14" s="193"/>
-      <c r="E14" s="285"/>
-      <c r="F14" s="265"/>
-      <c r="G14" s="264"/>
-      <c r="H14" s="265"/>
-      <c r="I14" s="273"/>
-      <c r="J14" s="265"/>
-      <c r="K14" s="264"/>
-      <c r="L14" s="265"/>
-      <c r="M14" s="279"/>
-      <c r="N14" s="280"/>
+      <c r="E14" s="292"/>
+      <c r="F14" s="262"/>
+      <c r="G14" s="261"/>
+      <c r="H14" s="262"/>
+      <c r="I14" s="298"/>
+      <c r="J14" s="262"/>
+      <c r="K14" s="261"/>
+      <c r="L14" s="262"/>
+      <c r="M14" s="283"/>
+      <c r="N14" s="284"/>
       <c r="O14" s="196"/>
-      <c r="P14" s="264"/>
-      <c r="Q14" s="265"/>
+      <c r="P14" s="261"/>
+      <c r="Q14" s="262"/>
       <c r="R14" s="195"/>
-      <c r="S14" s="279"/>
-      <c r="T14" s="280"/>
+      <c r="S14" s="283"/>
+      <c r="T14" s="284"/>
       <c r="U14" s="196"/>
-      <c r="V14" s="264"/>
-      <c r="W14" s="265"/>
+      <c r="V14" s="261"/>
+      <c r="W14" s="262"/>
       <c r="X14" s="195"/>
-      <c r="Y14" s="279"/>
-      <c r="Z14" s="280"/>
+      <c r="Y14" s="283"/>
+      <c r="Z14" s="284"/>
       <c r="AA14" s="196"/>
-      <c r="AB14" s="264"/>
-      <c r="AC14" s="265"/>
+      <c r="AB14" s="261"/>
+      <c r="AC14" s="262"/>
       <c r="AD14" s="195"/>
-      <c r="AE14" s="279"/>
-      <c r="AF14" s="280"/>
+      <c r="AE14" s="283"/>
+      <c r="AF14" s="284"/>
       <c r="AG14" s="196"/>
-      <c r="AH14" s="264"/>
-      <c r="AI14" s="265"/>
+      <c r="AH14" s="261"/>
+      <c r="AI14" s="262"/>
       <c r="AJ14" s="195"/>
     </row>
     <row r="15" spans="1:36" s="118" customFormat="1" ht="37.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -10059,7 +10056,7 @@
       <c r="C16" s="160" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="282" t="s">
+      <c r="D16" s="288" t="s">
         <v>285</v>
       </c>
       <c r="E16" s="176">
@@ -10151,7 +10148,7 @@
       <c r="C17" s="160" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="283"/>
+      <c r="D17" s="289"/>
       <c r="E17" s="167">
         <v>3</v>
       </c>
@@ -12932,11 +12929,11 @@
       <c r="X48" s="170">
         <v>1</v>
       </c>
-      <c r="Y48" s="290" t="s">
+      <c r="Y48" s="263" t="s">
         <v>252</v>
       </c>
-      <c r="Z48" s="291"/>
-      <c r="AA48" s="292"/>
+      <c r="Z48" s="264"/>
+      <c r="AA48" s="265"/>
       <c r="AB48" s="170">
         <v>4</v>
       </c>
@@ -13018,9 +13015,9 @@
       <c r="X49" s="161">
         <v>4</v>
       </c>
-      <c r="Y49" s="293"/>
-      <c r="Z49" s="294"/>
-      <c r="AA49" s="295"/>
+      <c r="Y49" s="266"/>
+      <c r="Z49" s="267"/>
+      <c r="AA49" s="268"/>
       <c r="AB49" s="161">
         <v>7</v>
       </c>
@@ -13102,9 +13099,9 @@
       <c r="X50" s="150">
         <v>3</v>
       </c>
-      <c r="Y50" s="293"/>
-      <c r="Z50" s="294"/>
-      <c r="AA50" s="295"/>
+      <c r="Y50" s="266"/>
+      <c r="Z50" s="267"/>
+      <c r="AA50" s="268"/>
       <c r="AB50" s="150">
         <v>8</v>
       </c>
@@ -13184,9 +13181,9 @@
       <c r="X51" s="150">
         <v>3</v>
       </c>
-      <c r="Y51" s="293"/>
-      <c r="Z51" s="294"/>
-      <c r="AA51" s="295"/>
+      <c r="Y51" s="266"/>
+      <c r="Z51" s="267"/>
+      <c r="AA51" s="268"/>
       <c r="AB51" s="150">
         <v>7</v>
       </c>
@@ -13268,9 +13265,9 @@
       <c r="X52" s="150">
         <v>5</v>
       </c>
-      <c r="Y52" s="293"/>
-      <c r="Z52" s="294"/>
-      <c r="AA52" s="295"/>
+      <c r="Y52" s="266"/>
+      <c r="Z52" s="267"/>
+      <c r="AA52" s="268"/>
       <c r="AB52" s="150">
         <v>6</v>
       </c>
@@ -13352,9 +13349,9 @@
       <c r="X53" s="141">
         <v>8</v>
       </c>
-      <c r="Y53" s="293"/>
-      <c r="Z53" s="294"/>
-      <c r="AA53" s="295"/>
+      <c r="Y53" s="266"/>
+      <c r="Z53" s="267"/>
+      <c r="AA53" s="268"/>
       <c r="AB53" s="141">
         <v>11</v>
       </c>
@@ -13435,9 +13432,9 @@
       <c r="X54" s="141">
         <v>5</v>
       </c>
-      <c r="Y54" s="293"/>
-      <c r="Z54" s="294"/>
-      <c r="AA54" s="295"/>
+      <c r="Y54" s="266"/>
+      <c r="Z54" s="267"/>
+      <c r="AA54" s="268"/>
       <c r="AB54" s="141">
         <v>9</v>
       </c>
@@ -13519,9 +13516,9 @@
       <c r="X55" s="129">
         <v>7</v>
       </c>
-      <c r="Y55" s="293"/>
-      <c r="Z55" s="294"/>
-      <c r="AA55" s="295"/>
+      <c r="Y55" s="266"/>
+      <c r="Z55" s="267"/>
+      <c r="AA55" s="268"/>
       <c r="AB55" s="129">
         <v>10</v>
       </c>
@@ -13603,9 +13600,9 @@
       <c r="X56" s="170">
         <v>8</v>
       </c>
-      <c r="Y56" s="293"/>
-      <c r="Z56" s="294"/>
-      <c r="AA56" s="295"/>
+      <c r="Y56" s="266"/>
+      <c r="Z56" s="267"/>
+      <c r="AA56" s="268"/>
       <c r="AB56" s="170">
         <v>8</v>
       </c>
@@ -13687,9 +13684,9 @@
       <c r="X57" s="161">
         <v>6</v>
       </c>
-      <c r="Y57" s="293"/>
-      <c r="Z57" s="294"/>
-      <c r="AA57" s="295"/>
+      <c r="Y57" s="266"/>
+      <c r="Z57" s="267"/>
+      <c r="AA57" s="268"/>
       <c r="AB57" s="161">
         <v>9</v>
       </c>
@@ -13771,9 +13768,9 @@
       <c r="X58" s="150">
         <v>7</v>
       </c>
-      <c r="Y58" s="293"/>
-      <c r="Z58" s="294"/>
-      <c r="AA58" s="295"/>
+      <c r="Y58" s="266"/>
+      <c r="Z58" s="267"/>
+      <c r="AA58" s="268"/>
       <c r="AB58" s="150">
         <v>11</v>
       </c>
@@ -13857,9 +13854,9 @@
       <c r="X59" s="150">
         <v>6</v>
       </c>
-      <c r="Y59" s="293"/>
-      <c r="Z59" s="294"/>
-      <c r="AA59" s="295"/>
+      <c r="Y59" s="266"/>
+      <c r="Z59" s="267"/>
+      <c r="AA59" s="268"/>
       <c r="AB59" s="150">
         <v>9</v>
       </c>
@@ -13943,9 +13940,9 @@
       <c r="X60" s="150">
         <v>1</v>
       </c>
-      <c r="Y60" s="293"/>
-      <c r="Z60" s="294"/>
-      <c r="AA60" s="295"/>
+      <c r="Y60" s="266"/>
+      <c r="Z60" s="267"/>
+      <c r="AA60" s="268"/>
       <c r="AB60" s="150">
         <v>3</v>
       </c>
@@ -14029,9 +14026,9 @@
       <c r="X61" s="141">
         <v>0</v>
       </c>
-      <c r="Y61" s="293"/>
-      <c r="Z61" s="294"/>
-      <c r="AA61" s="295"/>
+      <c r="Y61" s="266"/>
+      <c r="Z61" s="267"/>
+      <c r="AA61" s="268"/>
       <c r="AB61" s="141">
         <v>3</v>
       </c>
@@ -14113,9 +14110,9 @@
       <c r="X62" s="141">
         <v>3</v>
       </c>
-      <c r="Y62" s="293"/>
-      <c r="Z62" s="294"/>
-      <c r="AA62" s="295"/>
+      <c r="Y62" s="266"/>
+      <c r="Z62" s="267"/>
+      <c r="AA62" s="268"/>
       <c r="AB62" s="141">
         <v>8</v>
       </c>
@@ -14197,9 +14194,9 @@
       <c r="X63" s="129">
         <v>3</v>
       </c>
-      <c r="Y63" s="296"/>
-      <c r="Z63" s="297"/>
-      <c r="AA63" s="298"/>
+      <c r="Y63" s="269"/>
+      <c r="Z63" s="270"/>
+      <c r="AA63" s="271"/>
       <c r="AB63" s="129">
         <v>9</v>
       </c>
@@ -18277,6 +18274,40 @@
     </row>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="P11:R11"/>
+    <mergeCell ref="P12:R12"/>
+    <mergeCell ref="P13:R13"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="AB12:AD12"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="V14:W14"/>
+    <mergeCell ref="S11:U11"/>
+    <mergeCell ref="S12:U12"/>
+    <mergeCell ref="S13:U13"/>
+    <mergeCell ref="S14:T14"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K13:L13"/>
     <mergeCell ref="AH14:AI14"/>
     <mergeCell ref="Y48:AA63"/>
     <mergeCell ref="AH11:AJ11"/>
@@ -18293,40 +18324,6 @@
     <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="AB11:AD11"/>
     <mergeCell ref="Y12:AA12"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="AB12:AD12"/>
-    <mergeCell ref="V11:X11"/>
-    <mergeCell ref="V12:X12"/>
-    <mergeCell ref="V13:X13"/>
-    <mergeCell ref="V14:W14"/>
-    <mergeCell ref="S11:U11"/>
-    <mergeCell ref="S12:U12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="M13:O13"/>
-    <mergeCell ref="P11:R11"/>
-    <mergeCell ref="P12:R12"/>
-    <mergeCell ref="P13:R13"/>
-    <mergeCell ref="S13:U13"/>
-    <mergeCell ref="S14:T14"/>
   </mergeCells>
   <conditionalFormatting sqref="C16:D16 C17 C18:D63">
     <cfRule type="cellIs" dxfId="49" priority="1" operator="equal">
@@ -19544,7 +19541,7 @@
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E2" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -20463,7 +20460,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C3" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="52"/>
@@ -20477,7 +20474,7 @@
     </row>
     <row r="4" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="300" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D4" s="303"/>
       <c r="E4" s="303"/>
@@ -20545,7 +20542,7 @@
         <v>29</v>
       </c>
       <c r="P6" s="237" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -23073,7 +23070,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C3" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3"/>
@@ -23087,7 +23084,7 @@
     </row>
     <row r="4" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="300" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D4" s="303"/>
       <c r="E4" s="303"/>
@@ -23155,7 +23152,7 @@
         <v>29</v>
       </c>
       <c r="P6" s="237" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -26115,7 +26112,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C3" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3"/>
@@ -26129,7 +26126,7 @@
     </row>
     <row r="4" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="300" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D4" s="303"/>
       <c r="E4" s="303"/>
@@ -26197,7 +26194,7 @@
         <v>29</v>
       </c>
       <c r="P6" s="237" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -29110,7 +29107,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C3" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3"/>
@@ -29125,7 +29122,7 @@
     </row>
     <row r="4" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="300" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D4" s="303"/>
       <c r="E4" s="303"/>
@@ -29193,7 +29190,7 @@
         <v>29</v>
       </c>
       <c r="P6" s="237" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -32112,7 +32109,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C3" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3"/>
@@ -32126,7 +32123,7 @@
     </row>
     <row r="4" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="300" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D4" s="303"/>
       <c r="E4" s="303"/>
@@ -32194,7 +32191,7 @@
         <v>29</v>
       </c>
       <c r="P6" s="237" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -35136,7 +35133,7 @@
         <v>8</v>
       </c>
       <c r="H1" s="242" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I1" s="241"/>
       <c r="J1" s="241"/>
@@ -35152,7 +35149,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C3" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D3" s="2"/>
       <c r="G3" s="4" t="s">
@@ -35164,7 +35161,7 @@
     </row>
     <row r="4" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="300" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D4" s="303"/>
       <c r="E4" s="303"/>
@@ -35233,7 +35230,7 @@
         <v>29</v>
       </c>
       <c r="P6" s="237" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -37809,7 +37806,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C3" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3"/>
@@ -37823,7 +37820,7 @@
     </row>
     <row r="4" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="300" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D4" s="303"/>
       <c r="E4" s="303"/>
@@ -37891,7 +37888,7 @@
         <v>29</v>
       </c>
       <c r="P6" s="237" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -46794,7 +46791,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C3" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3"/>
@@ -46808,7 +46805,7 @@
     </row>
     <row r="4" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="300" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D4" s="303"/>
       <c r="E4" s="303"/>
@@ -46818,7 +46815,7 @@
       <c r="I4" s="303"/>
       <c r="J4" s="240"/>
       <c r="K4" s="303" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L4" s="303"/>
       <c r="M4" s="303"/>
@@ -46878,7 +46875,7 @@
         <v>29</v>
       </c>
       <c r="P6" s="237" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -49803,7 +49800,7 @@
         <v>227</v>
       </c>
       <c r="B1" s="116" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.25">
@@ -50226,28 +50223,28 @@
         <v>231</v>
       </c>
       <c r="F1" s="116" t="s">
+        <v>311</v>
+      </c>
+      <c r="G1" s="116" t="s">
         <v>312</v>
       </c>
-      <c r="G1" s="116" t="s">
+      <c r="H1" s="116" t="s">
         <v>313</v>
       </c>
-      <c r="H1" s="116" t="s">
+      <c r="I1" s="116" t="s">
         <v>314</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="J1" s="116" t="s">
         <v>315</v>
       </c>
-      <c r="J1" s="116" t="s">
+      <c r="K1" s="116" t="s">
         <v>316</v>
       </c>
-      <c r="K1" s="116" t="s">
+      <c r="L1" s="116" t="s">
         <v>317</v>
       </c>
-      <c r="L1" s="116" t="s">
+      <c r="M1" s="116" t="s">
         <v>318</v>
-      </c>
-      <c r="M1" s="116" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" x14ac:dyDescent="0.25">
